--- a/artfynd/A 30112-2025 artfynd.xlsx
+++ b/artfynd/A 30112-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>126022921</v>
       </c>
       <c r="B4" t="n">
-        <v>98667</v>
+        <v>98671</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>126022920</v>
       </c>
       <c r="B5" t="n">
-        <v>98667</v>
+        <v>98671</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30112-2025 artfynd.xlsx
+++ b/artfynd/A 30112-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>126022921</v>
       </c>
       <c r="B4" t="n">
-        <v>98671</v>
+        <v>98672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>126022920</v>
       </c>
       <c r="B5" t="n">
-        <v>98671</v>
+        <v>98672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30112-2025 artfynd.xlsx
+++ b/artfynd/A 30112-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>126022921</v>
       </c>
       <c r="B4" t="n">
-        <v>98672</v>
+        <v>98674</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>126022920</v>
       </c>
       <c r="B5" t="n">
-        <v>98672</v>
+        <v>98674</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30112-2025 artfynd.xlsx
+++ b/artfynd/A 30112-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>126022921</v>
       </c>
       <c r="B4" t="n">
-        <v>98674</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>126022920</v>
       </c>
       <c r="B5" t="n">
-        <v>98674</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30112-2025 artfynd.xlsx
+++ b/artfynd/A 30112-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>126022921</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>126022920</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30112-2025 artfynd.xlsx
+++ b/artfynd/A 30112-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>126022921</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>126022920</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98682</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30112-2025 artfynd.xlsx
+++ b/artfynd/A 30112-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>126022921</v>
       </c>
       <c r="B4" t="n">
-        <v>98682</v>
+        <v>98685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>126022920</v>
       </c>
       <c r="B5" t="n">
-        <v>98682</v>
+        <v>98685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30112-2025 artfynd.xlsx
+++ b/artfynd/A 30112-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>126022921</v>
       </c>
       <c r="B4" t="n">
-        <v>98685</v>
+        <v>98694</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>126022920</v>
       </c>
       <c r="B5" t="n">
-        <v>98685</v>
+        <v>98694</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30112-2025 artfynd.xlsx
+++ b/artfynd/A 30112-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104451209</v>
+        <v>81142501</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,29 +695,37 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bräcke, Jmt</t>
+          <t>Storåsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556601.5925261303</v>
+        <v>556576</v>
       </c>
       <c r="R2" t="n">
-        <v>6972275.073814138</v>
+        <v>6972372</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2019-10-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2019-10-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,53 +765,53 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104451211</v>
+        <v>104451209</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556526.488130215</v>
+        <v>556602</v>
       </c>
       <c r="R3" t="n">
-        <v>6972522.044971293</v>
+        <v>6972275</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126022921</v>
+        <v>126022890</v>
       </c>
       <c r="B4" t="n">
-        <v>98694</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219880</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556471</v>
+        <v>556582</v>
       </c>
       <c r="R4" t="n">
-        <v>6972489</v>
+        <v>6972362</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,32 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126022920</v>
+        <v>126022891</v>
       </c>
       <c r="B5" t="n">
-        <v>98694</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219880</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556397</v>
+        <v>556639</v>
       </c>
       <c r="R5" t="n">
-        <v>6972476</v>
+        <v>6972253</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1092,6 +1085,1036 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>81142498</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>556576</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6972372</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-10-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-10-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>81142499</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>556621</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6972249</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-10-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-10-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark av gammal, senvuxen gran</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126022889</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>556373</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6972407</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126022888</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>556630</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6972255</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosöksspår</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126022885</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>556630</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6972265</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hane</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126022920</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>556397</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6972476</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126022921</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>556471</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6972489</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104451210</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bräcke, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>556569</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6972522</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>104451211</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bräcke, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>556527</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6972522</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126022895</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>556585</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6972326</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30112-2025 artfynd.xlsx
+++ b/artfynd/A 30112-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142501</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104451209</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022890</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022891</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142498</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142499</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022889</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,6 +1546,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022888</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1608,6 +1653,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022885</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1705,6 +1755,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022920</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1802,6 +1857,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022921</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1910,6 +1970,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104451210</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2018,6 +2083,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104451211</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2115,8 +2185,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022895</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>